--- a/data-raw/musical_instruments.xlsx
+++ b/data-raw/musical_instruments.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/musicassessr/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1219A6A-3B30-F84C-BDDA-CA24C8CD5C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2FDBFC-A931-994B-BA51-22C63FCDADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="1280" windowWidth="27640" windowHeight="16860" xr2:uid="{CB7537FB-C9CF-C142-AE58-74683695060A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
   <si>
     <t>Piano</t>
   </si>
@@ -316,6 +316,21 @@
   </si>
   <si>
     <t>Elektriskā ģitāra</t>
+  </si>
+  <si>
+    <t>french_horn</t>
+  </si>
+  <si>
+    <t>French Horn</t>
+  </si>
+  <si>
+    <t>Corno</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Waldhorn</t>
+  </si>
+  <si>
+    <t>Mežrags</t>
   </si>
 </sst>
 </file>
@@ -703,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFE8AF5-2A59-E340-94E0-F3103F65052D}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" style="2" customWidth="1"/>
@@ -1520,6 +1535,41 @@
         <v>73</v>
       </c>
     </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="2">
+        <v>34</v>
+      </c>
+      <c r="G24" s="2">
+        <v>80</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-7</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="2">
+        <v>46</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/musical_instruments.xlsx
+++ b/data-raw/musical_instruments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebsilas/musicassessr/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2FDBFC-A931-994B-BA51-22C63FCDADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{306D3FE9-D709-C947-BBF0-90B3003283B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="1280" windowWidth="27640" windowHeight="16860" xr2:uid="{CB7537FB-C9CF-C142-AE58-74683695060A}"/>
   </bookViews>
@@ -1564,7 +1564,7 @@
         <v>34</v>
       </c>
       <c r="J24" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>73</v>
